--- a/check.xlsx
+++ b/check.xlsx
@@ -1690,7 +1690,7 @@
       <c r="AC4" s="61" t="n"/>
       <c r="AD4" s="63" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="AE4" s="60" t="n"/>
@@ -1740,7 +1740,7 @@
       <c r="AC5" s="61" t="n"/>
       <c r="AD5" s="67" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AE5" s="60" t="n"/>
@@ -1788,7 +1788,7 @@
       <c r="AA6" s="61" t="n"/>
       <c r="AB6" s="68" t="inlineStr">
         <is>
-          <t>5979FKM</t>
+          <t>7450HDK</t>
         </is>
       </c>
       <c r="AC6" s="60" t="n"/>
